--- a/Fuerza Docente.xlsx
+++ b/Fuerza Docente.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_79C8EE1A15B34410B0C00D41484231440100DA06" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30889A79-CECC-4F3D-AB7E-C4A160C358F9}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93754A15-9327-6F4B-A9F6-1895C6297301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="19020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="25600" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -297,9 +302,6 @@
     <t>anaisabel.munoz</t>
   </si>
   <si>
-    <t>MUÑOZ MONTALVO, ANA ISABEL</t>
-  </si>
-  <si>
     <t>0.0 % (-165 h)</t>
   </si>
   <si>
@@ -442,13 +444,16 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>MUÑOZ MONTALVO, ANA I.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -457,6 +462,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -479,14 +490,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,7 +517,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -802,24 +814,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="49.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="28.5" customWidth="1"/>
+    <col min="4" max="4" width="49.5" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="59.42578125" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" customWidth="1"/>
-    <col min="9" max="9" width="27.28515625" customWidth="1"/>
-    <col min="10" max="11" width="16.85546875" customWidth="1"/>
-    <col min="12" max="12" width="7.85546875" customWidth="1"/>
-    <col min="13" max="13" width="6.42578125" customWidth="1"/>
-    <col min="14" max="14" width="22.140625" customWidth="1"/>
+    <col min="6" max="6" width="59.5" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19.5" customWidth="1"/>
+    <col min="9" max="9" width="27.33203125" customWidth="1"/>
+    <col min="10" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="7.83203125" customWidth="1"/>
+    <col min="13" max="13" width="6.5" customWidth="1"/>
+    <col min="14" max="14" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -837,7 +849,7 @@
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -881,7 +893,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -922,7 +934,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -963,7 +975,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1004,7 +1016,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1045,7 +1057,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1086,7 +1098,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1127,7 +1139,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1168,7 +1180,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1209,7 +1221,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1250,7 +1262,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1291,7 +1303,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1332,7 +1344,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1373,7 +1385,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1414,7 +1426,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1455,7 +1467,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1496,7 +1508,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1537,7 +1549,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1578,7 +1590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1619,7 +1631,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -1660,7 +1672,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -1701,7 +1713,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -1742,7 +1754,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1783,7 +1795,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -1824,7 +1836,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -1865,7 +1877,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -1906,7 +1918,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -1947,7 +1959,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -1988,7 +2000,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -1998,8 +2010,8 @@
       <c r="C30" t="s">
         <v>87</v>
       </c>
-      <c r="D30" t="s">
-        <v>88</v>
+      <c r="D30" s="5" t="s">
+        <v>136</v>
       </c>
       <c r="F30" t="s">
         <v>19</v>
@@ -2026,21 +2038,21 @@
         <v>0</v>
       </c>
       <c r="N30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>90</v>
-      </c>
-      <c r="D31" t="s">
-        <v>91</v>
       </c>
       <c r="F31" t="s">
         <v>23</v>
@@ -2070,7 +2082,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -2078,10 +2090,10 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" t="s">
         <v>92</v>
-      </c>
-      <c r="D32" t="s">
-        <v>93</v>
       </c>
       <c r="F32" t="s">
         <v>19</v>
@@ -2111,7 +2123,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -2119,10 +2131,10 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" t="s">
         <v>94</v>
-      </c>
-      <c r="D33" t="s">
-        <v>95</v>
       </c>
       <c r="F33" t="s">
         <v>19</v>
@@ -2149,21 +2161,21 @@
         <v>0</v>
       </c>
       <c r="N33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>97</v>
-      </c>
-      <c r="D34" t="s">
-        <v>98</v>
       </c>
       <c r="F34" t="s">
         <v>73</v>
@@ -2193,7 +2205,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -2201,10 +2213,10 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" t="s">
         <v>99</v>
-      </c>
-      <c r="D35" t="s">
-        <v>100</v>
       </c>
       <c r="F35" t="s">
         <v>73</v>
@@ -2234,7 +2246,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -2242,10 +2254,10 @@
         <v>16</v>
       </c>
       <c r="C36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" t="s">
         <v>101</v>
-      </c>
-      <c r="D36" t="s">
-        <v>102</v>
       </c>
       <c r="F36" t="s">
         <v>19</v>
@@ -2272,24 +2284,24 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>104</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
         <v>105</v>
-      </c>
-      <c r="F37" t="s">
-        <v>106</v>
       </c>
       <c r="G37" s="2">
         <v>90</v>
@@ -2313,21 +2325,21 @@
         <v>0</v>
       </c>
       <c r="N37" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>108</v>
-      </c>
-      <c r="D38" t="s">
-        <v>109</v>
       </c>
       <c r="F38" t="s">
         <v>23</v>
@@ -2357,7 +2369,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -2365,10 +2377,10 @@
         <v>16</v>
       </c>
       <c r="C39" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" t="s">
         <v>110</v>
-      </c>
-      <c r="D39" t="s">
-        <v>111</v>
       </c>
       <c r="F39" t="s">
         <v>43</v>
@@ -2395,21 +2407,21 @@
         <v>0</v>
       </c>
       <c r="N39" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>113</v>
-      </c>
-      <c r="D40" t="s">
-        <v>114</v>
       </c>
       <c r="F40" t="s">
         <v>19</v>
@@ -2436,10 +2448,10 @@
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -2447,10 +2459,10 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" t="s">
         <v>115</v>
-      </c>
-      <c r="D41" t="s">
-        <v>116</v>
       </c>
       <c r="F41" t="s">
         <v>23</v>
@@ -2480,7 +2492,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -2488,10 +2500,10 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" t="s">
         <v>117</v>
-      </c>
-      <c r="D42" t="s">
-        <v>118</v>
       </c>
       <c r="F42" t="s">
         <v>43</v>
@@ -2521,7 +2533,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -2529,10 +2541,10 @@
         <v>16</v>
       </c>
       <c r="C43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" t="s">
         <v>119</v>
-      </c>
-      <c r="D43" t="s">
-        <v>120</v>
       </c>
       <c r="F43" t="s">
         <v>19</v>
@@ -2559,21 +2571,21 @@
         <v>0</v>
       </c>
       <c r="N43" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>122</v>
-      </c>
-      <c r="D44" t="s">
-        <v>123</v>
       </c>
       <c r="F44" t="s">
         <v>19</v>
@@ -2603,7 +2615,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -2611,13 +2623,13 @@
         <v>16</v>
       </c>
       <c r="C45" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" t="s">
         <v>124</v>
       </c>
-      <c r="D45" t="s">
+      <c r="F45" t="s">
         <v>125</v>
-      </c>
-      <c r="F45" t="s">
-        <v>126</v>
       </c>
       <c r="G45" s="2">
         <v>240</v>
@@ -2644,7 +2656,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -2652,10 +2664,10 @@
         <v>16</v>
       </c>
       <c r="C46" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" t="s">
         <v>127</v>
-      </c>
-      <c r="D46" t="s">
-        <v>128</v>
       </c>
       <c r="F46" t="s">
         <v>29</v>
@@ -2682,21 +2694,21 @@
         <v>0</v>
       </c>
       <c r="N46" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>130</v>
-      </c>
-      <c r="D47" t="s">
-        <v>131</v>
       </c>
       <c r="F47" t="s">
         <v>73</v>
@@ -2726,7 +2738,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -2734,10 +2746,10 @@
         <v>16</v>
       </c>
       <c r="C48" t="s">
+        <v>131</v>
+      </c>
+      <c r="D48" t="s">
         <v>132</v>
-      </c>
-      <c r="D48" t="s">
-        <v>133</v>
       </c>
       <c r="F48" t="s">
         <v>43</v>
@@ -2767,7 +2779,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -2775,10 +2787,10 @@
         <v>16</v>
       </c>
       <c r="C49" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" t="s">
         <v>134</v>
-      </c>
-      <c r="D49" t="s">
-        <v>135</v>
       </c>
       <c r="F49" t="s">
         <v>40</v>
@@ -2808,9 +2820,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L51" s="2">
         <f>SUM(L3:L49)</f>

--- a/Fuerza Docente.xlsx
+++ b/Fuerza Docente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93754A15-9327-6F4B-A9F6-1895C6297301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3AF535-0317-F947-B563-769A6DB4BB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="25600" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="134">
   <si>
     <t>Fuerza Docente</t>
   </si>
@@ -186,15 +186,6 @@
   </si>
   <si>
     <t>FLORES ÁLVAREZ, JULIO</t>
-  </si>
-  <si>
-    <t>alessandra.gallinari</t>
-  </si>
-  <si>
-    <t>GALLINARI BIRAGHI, ALESSANDRA</t>
-  </si>
-  <si>
-    <t>Titular Escuela Universitaria - Tiempo completo, 12 horas lect.semanales</t>
   </si>
   <si>
     <t>alejandro.garciadelamo</t>
@@ -494,11 +485,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -813,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -832,22 +823,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1358,13 +1349,13 @@
         <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="G14" s="2">
         <v>240</v>
       </c>
       <c r="H14" s="2">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
@@ -1373,16 +1364,16 @@
         <v>0</v>
       </c>
       <c r="K14" s="2">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="L14" s="2">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="M14" s="2">
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -1393,37 +1384,37 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
         <v>53</v>
       </c>
-      <c r="D15" t="s">
-        <v>54</v>
-      </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G15" s="2">
         <v>240</v>
       </c>
       <c r="H15" s="2">
-        <v>-45</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="K15" s="2">
-        <v>-45</v>
+        <v>-120</v>
       </c>
       <c r="L15" s="2">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="M15" s="2">
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -1434,37 +1425,37 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
         <v>55</v>
       </c>
-      <c r="D16" t="s">
-        <v>56</v>
-      </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G16" s="2">
         <v>240</v>
       </c>
       <c r="H16" s="2">
-        <v>-60</v>
+        <v>-15</v>
       </c>
       <c r="I16" s="2">
         <v>0</v>
       </c>
       <c r="J16" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2">
-        <v>-120</v>
+        <v>-15</v>
       </c>
       <c r="L16" s="2">
-        <v>120</v>
+        <v>225</v>
       </c>
       <c r="M16" s="2">
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -1475,37 +1466,37 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
         <v>57</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
         <v>58</v>
-      </c>
-      <c r="F17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="2">
-        <v>240</v>
-      </c>
-      <c r="H17" s="2">
-        <v>-15</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0</v>
-      </c>
-      <c r="K17" s="2">
-        <v>-15</v>
-      </c>
-      <c r="L17" s="2">
-        <v>225</v>
-      </c>
-      <c r="M17" s="2">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -1522,10 +1513,10 @@
         <v>60</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G18" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
@@ -1540,13 +1531,13 @@
         <v>0</v>
       </c>
       <c r="L18" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M18" s="2">
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -1557,37 +1548,37 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" t="s">
         <v>62</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="2">
+        <v>240</v>
+      </c>
+      <c r="H19" s="2">
+        <v>-30</v>
+      </c>
+      <c r="I19" s="2">
+        <v>-20</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <v>-50</v>
+      </c>
+      <c r="L19" s="2">
+        <v>190</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
         <v>63</v>
-      </c>
-      <c r="F19" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="2">
-        <v>180</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2">
-        <v>0</v>
-      </c>
-      <c r="L19" s="2">
-        <v>180</v>
-      </c>
-      <c r="M19" s="2">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -1604,31 +1595,31 @@
         <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G20" s="2">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="H20" s="2">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2">
         <v>0</v>
       </c>
       <c r="K20" s="2">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="M20" s="2">
         <v>0</v>
       </c>
       <c r="N20" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
@@ -1639,16 +1630,16 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" t="s">
         <v>67</v>
       </c>
-      <c r="D21" t="s">
-        <v>68</v>
-      </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G21" s="2">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="H21" s="2">
         <v>0</v>
@@ -1663,13 +1654,13 @@
         <v>0</v>
       </c>
       <c r="L21" s="2">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="M21" s="2">
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
@@ -1680,19 +1671,19 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
         <v>69</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>70</v>
       </c>
-      <c r="F22" t="s">
-        <v>23</v>
-      </c>
       <c r="G22" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H22" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
@@ -1701,16 +1692,16 @@
         <v>0</v>
       </c>
       <c r="K22" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L22" s="2">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="M22" s="2">
         <v>0</v>
       </c>
       <c r="N22" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
@@ -1727,7 +1718,7 @@
         <v>72</v>
       </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="G23" s="2">
         <v>240</v>
@@ -1762,19 +1753,19 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
         <v>74</v>
       </c>
-      <c r="D24" t="s">
-        <v>75</v>
-      </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G24" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H24" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
@@ -1783,16 +1774,16 @@
         <v>0</v>
       </c>
       <c r="K24" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="M24" s="2">
         <v>0</v>
       </c>
       <c r="N24" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
@@ -1803,16 +1794,16 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" t="s">
         <v>76</v>
       </c>
-      <c r="D25" t="s">
-        <v>77</v>
-      </c>
       <c r="F25" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H25" s="2">
         <v>0</v>
@@ -1827,13 +1818,13 @@
         <v>0</v>
       </c>
       <c r="L25" s="2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2">
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -1844,16 +1835,16 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" t="s">
         <v>78</v>
       </c>
-      <c r="D26" t="s">
-        <v>79</v>
-      </c>
       <c r="F26" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="G26" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
@@ -1868,13 +1859,13 @@
         <v>0</v>
       </c>
       <c r="L26" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M26" s="2">
         <v>0</v>
       </c>
       <c r="N26" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -1885,16 +1876,16 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" t="s">
         <v>80</v>
       </c>
-      <c r="D27" t="s">
-        <v>81</v>
-      </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G27" s="2">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
@@ -1909,13 +1900,13 @@
         <v>0</v>
       </c>
       <c r="L27" s="2">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="M27" s="2">
         <v>0</v>
       </c>
       <c r="N27" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -1926,16 +1917,16 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" t="s">
         <v>82</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>83</v>
       </c>
-      <c r="F28" t="s">
-        <v>29</v>
-      </c>
       <c r="G28" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H28" s="2">
         <v>0</v>
@@ -1950,13 +1941,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2">
         <v>0</v>
       </c>
       <c r="N28" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
@@ -1969,35 +1960,35 @@
       <c r="C29" t="s">
         <v>84</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="2">
+        <v>240</v>
+      </c>
+      <c r="H29" s="2">
+        <v>-45</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>-30</v>
+      </c>
+      <c r="K29" s="2">
+        <v>-75</v>
+      </c>
+      <c r="L29" s="2">
+        <v>165</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
         <v>85</v>
-      </c>
-      <c r="F29" t="s">
-        <v>86</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2">
-        <v>0</v>
-      </c>
-      <c r="K29" s="2">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2">
-        <v>0</v>
-      </c>
-      <c r="M29" s="2">
-        <v>0</v>
-      </c>
-      <c r="N29" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
@@ -2008,37 +1999,37 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" t="s">
         <v>87</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="F30" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G30" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H30" s="2">
-        <v>-45</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
         <v>0</v>
       </c>
       <c r="J30" s="2">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="K30" s="2">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="M30" s="2">
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
@@ -2049,19 +2040,19 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" t="s">
         <v>89</v>
       </c>
-      <c r="D31" t="s">
-        <v>90</v>
-      </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G31" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H31" s="2">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="I31" s="2">
         <v>0</v>
@@ -2070,16 +2061,16 @@
         <v>0</v>
       </c>
       <c r="K31" s="2">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="L31" s="2">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="M31" s="2">
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
@@ -2090,10 +2081,10 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" t="s">
         <v>91</v>
-      </c>
-      <c r="D32" t="s">
-        <v>92</v>
       </c>
       <c r="F32" t="s">
         <v>19</v>
@@ -2102,25 +2093,25 @@
         <v>240</v>
       </c>
       <c r="H32" s="2">
-        <v>-45</v>
+        <v>-60</v>
       </c>
       <c r="I32" s="2">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="J32" s="2">
         <v>0</v>
       </c>
       <c r="K32" s="2">
-        <v>-45</v>
+        <v>-80</v>
       </c>
       <c r="L32" s="2">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="M32" s="2">
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -2137,31 +2128,31 @@
         <v>94</v>
       </c>
       <c r="F33" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="G33" s="2">
         <v>240</v>
       </c>
       <c r="H33" s="2">
-        <v>-60</v>
+        <v>-15</v>
       </c>
       <c r="I33" s="2">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
       </c>
       <c r="K33" s="2">
-        <v>-80</v>
+        <v>-15</v>
       </c>
       <c r="L33" s="2">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="M33" s="2">
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
@@ -2172,19 +2163,19 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" t="s">
         <v>96</v>
       </c>
-      <c r="D34" t="s">
-        <v>97</v>
-      </c>
       <c r="F34" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G34" s="2">
         <v>240</v>
       </c>
       <c r="H34" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="I34" s="2">
         <v>0</v>
@@ -2193,16 +2184,16 @@
         <v>0</v>
       </c>
       <c r="K34" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M34" s="2">
         <v>0</v>
       </c>
       <c r="N34" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -2213,37 +2204,37 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" t="s">
         <v>98</v>
       </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="2">
+        <v>240</v>
+      </c>
+      <c r="H35" s="2">
+        <v>-30</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2">
+        <v>-30</v>
+      </c>
+      <c r="L35" s="2">
+        <v>210</v>
+      </c>
+      <c r="M35" s="2">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
         <v>99</v>
-      </c>
-      <c r="F35" t="s">
-        <v>73</v>
-      </c>
-      <c r="G35" s="2">
-        <v>240</v>
-      </c>
-      <c r="H35" s="2">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2">
-        <v>0</v>
-      </c>
-      <c r="J35" s="2">
-        <v>0</v>
-      </c>
-      <c r="K35" s="2">
-        <v>0</v>
-      </c>
-      <c r="L35" s="2">
-        <v>240</v>
-      </c>
-      <c r="M35" s="2">
-        <v>0</v>
-      </c>
-      <c r="N35" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
@@ -2260,13 +2251,13 @@
         <v>101</v>
       </c>
       <c r="F36" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="G36" s="2">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="H36" s="2">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="I36" s="2">
         <v>0</v>
@@ -2275,16 +2266,16 @@
         <v>0</v>
       </c>
       <c r="K36" s="2">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="M36" s="2">
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -2295,16 +2286,16 @@
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F37" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="G37" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -2319,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="L37" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M37" s="2">
         <v>0</v>
       </c>
       <c r="N37" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
@@ -2336,37 +2327,37 @@
         <v>16</v>
       </c>
       <c r="C38" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" t="s">
         <v>107</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G38" s="2">
+        <v>240</v>
+      </c>
+      <c r="H38" s="2">
+        <v>-60</v>
+      </c>
+      <c r="I38" s="2">
+        <v>-5</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2">
+        <v>-65</v>
+      </c>
+      <c r="L38" s="2">
+        <v>175</v>
+      </c>
+      <c r="M38" s="2">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
         <v>108</v>
-      </c>
-      <c r="F38" t="s">
-        <v>23</v>
-      </c>
-      <c r="G38" s="2">
-        <v>180</v>
-      </c>
-      <c r="H38" s="2">
-        <v>0</v>
-      </c>
-      <c r="I38" s="2">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2">
-        <v>0</v>
-      </c>
-      <c r="K38" s="2">
-        <v>0</v>
-      </c>
-      <c r="L38" s="2">
-        <v>180</v>
-      </c>
-      <c r="M38" s="2">
-        <v>0</v>
-      </c>
-      <c r="N38" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
@@ -2383,7 +2374,7 @@
         <v>110</v>
       </c>
       <c r="F39" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G39" s="2">
         <v>240</v>
@@ -2392,22 +2383,22 @@
         <v>-60</v>
       </c>
       <c r="I39" s="2">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="J39" s="2">
         <v>0</v>
       </c>
       <c r="K39" s="2">
-        <v>-65</v>
+        <v>-80</v>
       </c>
       <c r="L39" s="2">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="M39" s="2">
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
@@ -2418,37 +2409,37 @@
         <v>16</v>
       </c>
       <c r="C40" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" t="s">
         <v>112</v>
       </c>
-      <c r="D40" t="s">
-        <v>113</v>
-      </c>
       <c r="F40" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G40" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H40" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I40" s="2">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="J40" s="2">
         <v>0</v>
       </c>
       <c r="K40" s="2">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="M40" s="2">
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
@@ -2459,19 +2450,19 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" t="s">
         <v>114</v>
       </c>
-      <c r="D41" t="s">
-        <v>115</v>
-      </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G41" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H41" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I41" s="2">
         <v>0</v>
@@ -2480,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="L41" s="2">
         <v>180</v>
@@ -2500,13 +2491,13 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" t="s">
         <v>116</v>
       </c>
-      <c r="D42" t="s">
-        <v>117</v>
-      </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G42" s="2">
         <v>240</v>
@@ -2515,22 +2506,22 @@
         <v>-60</v>
       </c>
       <c r="I42" s="2">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="J42" s="2">
         <v>0</v>
       </c>
       <c r="K42" s="2">
-        <v>-60</v>
+        <v>-84</v>
       </c>
       <c r="L42" s="2">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="M42" s="2">
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
@@ -2556,22 +2547,22 @@
         <v>-60</v>
       </c>
       <c r="I43" s="2">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="J43" s="2">
         <v>0</v>
       </c>
       <c r="K43" s="2">
-        <v>-84</v>
+        <v>-60</v>
       </c>
       <c r="L43" s="2">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="M43" s="2">
         <v>0</v>
       </c>
       <c r="N43" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
@@ -2582,19 +2573,19 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" t="s">
         <v>121</v>
       </c>
-      <c r="D44" t="s">
+      <c r="F44" t="s">
         <v>122</v>
       </c>
-      <c r="F44" t="s">
-        <v>19</v>
-      </c>
       <c r="G44" s="2">
         <v>240</v>
       </c>
       <c r="H44" s="2">
-        <v>-60</v>
+        <v>-15</v>
       </c>
       <c r="I44" s="2">
         <v>0</v>
@@ -2603,16 +2594,16 @@
         <v>0</v>
       </c>
       <c r="K44" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="M44" s="2">
         <v>0</v>
       </c>
       <c r="N44" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
@@ -2629,31 +2620,31 @@
         <v>124</v>
       </c>
       <c r="F45" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" s="2">
+        <v>100</v>
+      </c>
+      <c r="H45" s="2">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0</v>
+      </c>
+      <c r="K45" s="2">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2">
+        <v>100</v>
+      </c>
+      <c r="M45" s="2">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
         <v>125</v>
-      </c>
-      <c r="G45" s="2">
-        <v>240</v>
-      </c>
-      <c r="H45" s="2">
-        <v>-15</v>
-      </c>
-      <c r="I45" s="2">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2">
-        <v>0</v>
-      </c>
-      <c r="K45" s="2">
-        <v>0</v>
-      </c>
-      <c r="L45" s="2">
-        <v>225</v>
-      </c>
-      <c r="M45" s="2">
-        <v>0</v>
-      </c>
-      <c r="N45" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
@@ -2670,10 +2661,10 @@
         <v>127</v>
       </c>
       <c r="F46" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="G46" s="2">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -2688,13 +2679,13 @@
         <v>0</v>
       </c>
       <c r="L46" s="2">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="M46" s="2">
         <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
@@ -2705,19 +2696,19 @@
         <v>16</v>
       </c>
       <c r="C47" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" t="s">
         <v>129</v>
       </c>
-      <c r="D47" t="s">
-        <v>130</v>
-      </c>
       <c r="F47" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="G47" s="2">
         <v>240</v>
       </c>
       <c r="H47" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I47" s="2">
         <v>0</v>
@@ -2726,16 +2717,16 @@
         <v>0</v>
       </c>
       <c r="K47" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="L47" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="M47" s="2">
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
@@ -2746,22 +2737,22 @@
         <v>16</v>
       </c>
       <c r="C48" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" t="s">
         <v>131</v>
       </c>
-      <c r="D48" t="s">
-        <v>132</v>
-      </c>
       <c r="F48" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G48" s="2">
         <v>240</v>
       </c>
       <c r="H48" s="2">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2">
         <v>-60</v>
-      </c>
-      <c r="I48" s="2">
-        <v>0</v>
       </c>
       <c r="J48" s="2">
         <v>0</v>
@@ -2779,53 +2770,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="s">
-        <v>133</v>
-      </c>
-      <c r="D49" t="s">
-        <v>134</v>
-      </c>
-      <c r="F49" t="s">
-        <v>40</v>
-      </c>
-      <c r="G49" s="2">
-        <v>240</v>
-      </c>
-      <c r="H49" s="2">
-        <v>0</v>
-      </c>
-      <c r="I49" s="2">
-        <v>-60</v>
-      </c>
-      <c r="J49" s="2">
-        <v>0</v>
-      </c>
-      <c r="K49" s="2">
-        <v>-60</v>
-      </c>
-      <c r="L49" s="2">
-        <v>180</v>
-      </c>
-      <c r="M49" s="2">
-        <v>0</v>
-      </c>
-      <c r="N49" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="K51" t="s">
-        <v>135</v>
-      </c>
-      <c r="L51" s="2">
-        <f>SUM(L3:L49)</f>
+    <row r="50" spans="11:12" x14ac:dyDescent="0.2">
+      <c r="K50" t="s">
+        <v>132</v>
+      </c>
+      <c r="L50" s="2">
+        <f>SUM(L3:L48)</f>
         <v>7541</v>
       </c>
     </row>

--- a/Fuerza Docente.xlsx
+++ b/Fuerza Docente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3AF535-0317-F947-B563-769A6DB4BB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C636961-5126-A849-B3B8-9F4E62136E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="25600" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -892,37 +892,37 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G3" s="2">
         <v>240</v>
       </c>
       <c r="H3" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J3" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="K3" s="2">
-        <v>0</v>
+        <v>-125</v>
       </c>
       <c r="L3" s="2">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="M3" s="2">
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -933,37 +933,37 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G4" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H4" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J4" s="2">
         <v>0</v>
       </c>
       <c r="K4" s="2">
-        <v>0</v>
+        <v>-65</v>
       </c>
       <c r="L4" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="M4" s="2">
         <v>0</v>
       </c>
       <c r="N4" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -974,19 +974,19 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G5" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H5" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="L5" s="2">
         <v>180</v>
@@ -1015,37 +1015,37 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="H6" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="K6" s="2">
-        <v>0</v>
+        <v>-120</v>
       </c>
       <c r="L6" s="2">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="M6" s="2">
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -1056,19 +1056,19 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G7" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H7" s="2">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -1077,16 +1077,16 @@
         <v>0</v>
       </c>
       <c r="K7" s="2">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="L7" s="2">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="M7" s="2">
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -1097,19 +1097,19 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G8" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H8" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="L8" s="2">
         <v>180</v>
@@ -1138,10 +1138,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
         <v>19</v>
@@ -1150,7 +1150,7 @@
         <v>240</v>
       </c>
       <c r="H9" s="2">
-        <v>-15</v>
+        <v>-45</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -1159,16 +1159,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="2">
-        <v>-15</v>
+        <v>-45</v>
       </c>
       <c r="L9" s="2">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="M9" s="2">
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -1179,37 +1179,37 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G10" s="2">
         <v>240</v>
       </c>
       <c r="H10" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I10" s="2">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="J10" s="2">
         <v>0</v>
       </c>
       <c r="K10" s="2">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="L10" s="2">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="M10" s="2">
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -1220,13 +1220,13 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G11" s="2">
         <v>240</v>
@@ -1235,22 +1235,22 @@
         <v>-60</v>
       </c>
       <c r="I11" s="2">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="J11" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2">
-        <v>-125</v>
+        <v>-80</v>
       </c>
       <c r="L11" s="2">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="M11" s="2">
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -1261,19 +1261,19 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G12" s="2">
         <v>240</v>
       </c>
       <c r="H12" s="2">
-        <v>-45</v>
+        <v>-60</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
@@ -1282,16 +1282,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="2">
-        <v>-45</v>
+        <v>-60</v>
       </c>
       <c r="L12" s="2">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="M12" s="2">
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -1302,10 +1302,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>49</v>
+        <v>84</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>133</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -1314,25 +1314,25 @@
         <v>240</v>
       </c>
       <c r="H13" s="2">
-        <v>-60</v>
+        <v>-45</v>
       </c>
       <c r="I13" s="2">
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="K13" s="2">
-        <v>-60</v>
+        <v>-75</v>
       </c>
       <c r="L13" s="2">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="M13" s="2">
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -1343,10 +1343,10 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
@@ -1355,7 +1355,7 @@
         <v>240</v>
       </c>
       <c r="H14" s="2">
-        <v>-45</v>
+        <v>-60</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
@@ -1364,16 +1364,16 @@
         <v>0</v>
       </c>
       <c r="K14" s="2">
-        <v>-45</v>
+        <v>-60</v>
       </c>
       <c r="L14" s="2">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="M14" s="2">
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -1384,37 +1384,37 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G15" s="2">
         <v>240</v>
       </c>
       <c r="H15" s="2">
-        <v>-60</v>
+        <v>-45</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2">
-        <v>-120</v>
+        <v>-45</v>
       </c>
       <c r="L15" s="2">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="M15" s="2">
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -1425,10 +1425,10 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="F16" t="s">
         <v>19</v>
@@ -1437,7 +1437,7 @@
         <v>240</v>
       </c>
       <c r="H16" s="2">
-        <v>-15</v>
+        <v>-30</v>
       </c>
       <c r="I16" s="2">
         <v>0</v>
@@ -1446,16 +1446,16 @@
         <v>0</v>
       </c>
       <c r="K16" s="2">
-        <v>-15</v>
+        <v>-30</v>
       </c>
       <c r="L16" s="2">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="M16" s="2">
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -1466,37 +1466,37 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G17" s="2">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H17" s="2">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="J17" s="2">
         <v>0</v>
       </c>
       <c r="K17" s="2">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L17" s="2">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="M17" s="2">
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -1507,19 +1507,19 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G18" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H18" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="I18" s="2">
         <v>0</v>
@@ -1528,16 +1528,16 @@
         <v>0</v>
       </c>
       <c r="K18" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L18" s="2">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="M18" s="2">
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -1548,10 +1548,10 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="F19" t="s">
         <v>19</v>
@@ -1560,25 +1560,25 @@
         <v>240</v>
       </c>
       <c r="H19" s="2">
-        <v>-30</v>
+        <v>-60</v>
       </c>
       <c r="I19" s="2">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="J19" s="2">
         <v>0</v>
       </c>
       <c r="K19" s="2">
-        <v>-50</v>
+        <v>-84</v>
       </c>
       <c r="L19" s="2">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="M19" s="2">
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -1589,19 +1589,19 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G20" s="2">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="H20" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="I20" s="2">
         <v>0</v>
@@ -1610,16 +1610,16 @@
         <v>0</v>
       </c>
       <c r="K20" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L20" s="2">
-        <v>60</v>
+        <v>225</v>
       </c>
       <c r="M20" s="2">
         <v>0</v>
       </c>
       <c r="N20" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
@@ -1630,19 +1630,19 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G21" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H21" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="I21" s="2">
         <v>0</v>
@@ -1651,16 +1651,16 @@
         <v>0</v>
       </c>
       <c r="K21" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L21" s="2">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="M21" s="2">
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
@@ -1671,19 +1671,19 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="G22" s="2">
         <v>240</v>
       </c>
       <c r="H22" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
@@ -1692,16 +1692,16 @@
         <v>0</v>
       </c>
       <c r="K22" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M22" s="2">
         <v>0</v>
       </c>
       <c r="N22" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
@@ -1712,13 +1712,13 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="G23" s="2">
         <v>240</v>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2">
         <v>225</v>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
@@ -1753,19 +1753,19 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="F24" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H24" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="I24" s="2">
         <v>0</v>
@@ -1774,16 +1774,16 @@
         <v>0</v>
       </c>
       <c r="K24" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L24" s="2">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="M24" s="2">
         <v>0</v>
       </c>
       <c r="N24" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
@@ -1794,19 +1794,19 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F25" t="s">
         <v>70</v>
       </c>
       <c r="G25" s="2">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H25" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
@@ -1815,16 +1815,16 @@
         <v>0</v>
       </c>
       <c r="K25" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L25" s="2">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="M25" s="2">
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -1835,16 +1835,16 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
@@ -1859,13 +1859,13 @@
         <v>0</v>
       </c>
       <c r="L26" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="M26" s="2">
         <v>0</v>
       </c>
       <c r="N26" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -1876,16 +1876,16 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="F27" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
@@ -1900,13 +1900,13 @@
         <v>0</v>
       </c>
       <c r="L27" s="2">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="M27" s="2">
         <v>0</v>
       </c>
       <c r="N27" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -1917,16 +1917,16 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="F28" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="G28" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H28" s="2">
         <v>0</v>
@@ -1941,13 +1941,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M28" s="2">
         <v>0</v>
       </c>
       <c r="N28" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
@@ -1958,37 +1958,37 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>133</v>
+        <v>25</v>
+      </c>
+      <c r="D29" t="s">
+        <v>26</v>
       </c>
       <c r="F29" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G29" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H29" s="2">
-        <v>-45</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2">
         <v>0</v>
       </c>
       <c r="J29" s="2">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="K29" s="2">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="M29" s="2">
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
@@ -1999,16 +1999,16 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="F30" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G30" s="2">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
@@ -2023,13 +2023,13 @@
         <v>0</v>
       </c>
       <c r="L30" s="2">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="M30" s="2">
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
@@ -2040,19 +2040,19 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G31" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H31" s="2">
-        <v>-45</v>
+        <v>0</v>
       </c>
       <c r="I31" s="2">
         <v>0</v>
@@ -2061,16 +2061,16 @@
         <v>0</v>
       </c>
       <c r="K31" s="2">
-        <v>-45</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="M31" s="2">
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
@@ -2081,37 +2081,37 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G32" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H32" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2">
         <v>0</v>
       </c>
       <c r="K32" s="2">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="M32" s="2">
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -2122,37 +2122,37 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="G33" s="2">
         <v>240</v>
       </c>
       <c r="H33" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
       </c>
       <c r="K33" s="2">
-        <v>-15</v>
+        <v>-60</v>
       </c>
       <c r="L33" s="2">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="M33" s="2">
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
@@ -2163,16 +2163,16 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="F34" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="G34" s="2">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2">
         <v>0</v>
@@ -2187,13 +2187,13 @@
         <v>0</v>
       </c>
       <c r="L34" s="2">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2">
         <v>0</v>
       </c>
       <c r="N34" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -2204,19 +2204,19 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="F35" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G35" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H35" s="2">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="I35" s="2">
         <v>0</v>
@@ -2225,16 +2225,16 @@
         <v>0</v>
       </c>
       <c r="K35" s="2">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="M35" s="2">
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
@@ -2245,16 +2245,16 @@
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="D36" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="F36" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="G36" s="2">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H36" s="2">
         <v>0</v>
@@ -2269,13 +2269,13 @@
         <v>0</v>
       </c>
       <c r="L36" s="2">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="M36" s="2">
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -2286,10 +2286,10 @@
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="F37" t="s">
         <v>23</v>
@@ -2327,37 +2327,37 @@
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="F38" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G38" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H38" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I38" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
       </c>
       <c r="K38" s="2">
-        <v>-65</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M38" s="2">
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
@@ -2368,37 +2368,37 @@
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="D39" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="F39" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="G39" s="2">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H39" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I39" s="2">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="J39" s="2">
         <v>0</v>
       </c>
       <c r="K39" s="2">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2">
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
@@ -2409,10 +2409,10 @@
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="D40" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="F40" t="s">
         <v>23</v>
@@ -2450,19 +2450,19 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="D41" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="F41" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G41" s="2">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="H41" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I41" s="2">
         <v>0</v>
@@ -2471,16 +2471,16 @@
         <v>0</v>
       </c>
       <c r="K41" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="M41" s="2">
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -2491,37 +2491,37 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="G42" s="2">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H42" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I42" s="2">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="J42" s="2">
         <v>0</v>
       </c>
       <c r="K42" s="2">
-        <v>-84</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2">
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
@@ -2532,19 +2532,19 @@
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="D43" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="F43" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G43" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H43" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I43" s="2">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2">
         <v>180</v>
@@ -2573,19 +2573,19 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="G44" s="2">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="H44" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="I44" s="2">
         <v>0</v>
@@ -2597,13 +2597,13 @@
         <v>0</v>
       </c>
       <c r="L44" s="2">
-        <v>225</v>
+        <v>90</v>
       </c>
       <c r="M44" s="2">
         <v>0</v>
       </c>
       <c r="N44" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
@@ -2614,16 +2614,16 @@
         <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D45" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="F45" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G45" s="2">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -2638,13 +2638,13 @@
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="M45" s="2">
         <v>0</v>
       </c>
       <c r="N45" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
@@ -2655,16 +2655,16 @@
         <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D46" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="F46" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="G46" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -2679,13 +2679,13 @@
         <v>0</v>
       </c>
       <c r="L46" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="M46" s="2">
         <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
@@ -2696,19 +2696,19 @@
         <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D47" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F47" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G47" s="2">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="H47" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I47" s="2">
         <v>0</v>
@@ -2717,16 +2717,16 @@
         <v>0</v>
       </c>
       <c r="K47" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="M47" s="2">
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
@@ -2775,8 +2775,8 @@
         <v>132</v>
       </c>
       <c r="L50" s="2">
-        <f>SUM(L3:L48)</f>
-        <v>7541</v>
+        <f>SUM(L28:L48)</f>
+        <v>2710</v>
       </c>
     </row>
   </sheetData>

--- a/Fuerza Docente.xlsx
+++ b/Fuerza Docente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C636961-5126-A849-B3B8-9F4E62136E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC390EA-5438-704E-8186-4787FDA5985D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="25600" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="126">
   <si>
     <t>Fuerza Docente</t>
   </si>
@@ -206,15 +206,6 @@
     <t>GONZÁLEZ DE LA ALEJA GALLEGO, DAVID</t>
   </si>
   <si>
-    <t>mariaisabel.vasco</t>
-  </si>
-  <si>
-    <t>GONZÁLEZ VASCO, MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>-  % (0 h)</t>
-  </si>
-  <si>
     <t>maria.gomez.olvera</t>
   </si>
   <si>
@@ -263,12 +254,6 @@
     <t>MARTINI, LORENZO</t>
   </si>
   <si>
-    <t>cedric.mcampos</t>
-  </si>
-  <si>
-    <t>MARTÍNEZ CAMPOS, CÉDRIC</t>
-  </si>
-  <si>
     <t>elena.martinez</t>
   </si>
   <si>
@@ -279,15 +264,6 @@
   </si>
   <si>
     <t>MARÍN RODRÍGUEZ, FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>gabriel.mindlin</t>
-  </si>
-  <si>
-    <t>MINDLIN, BERNARDO GABRIEL</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>anaisabel.munoz</t>
@@ -804,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -933,10 +909,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F4" t="s">
         <v>43</v>
@@ -963,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -974,10 +950,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F5" t="s">
         <v>43</v>
@@ -1097,10 +1073,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s">
         <v>43</v>
@@ -1179,10 +1155,10 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
@@ -1209,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -1220,10 +1196,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
         <v>19</v>
@@ -1250,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -1302,10 +1278,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -1332,7 +1308,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -1343,10 +1319,10 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
@@ -1384,10 +1360,10 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F15" t="s">
         <v>19</v>
@@ -1425,10 +1401,10 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
         <v>19</v>
@@ -1455,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -1466,10 +1442,10 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F17" t="s">
         <v>19</v>
@@ -1496,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -1507,10 +1483,10 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s">
         <v>19</v>
@@ -1548,10 +1524,10 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F19" t="s">
         <v>19</v>
@@ -1578,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -1712,13 +1688,13 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F23" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G23" s="2">
         <v>240</v>
@@ -1753,13 +1729,13 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G24" s="2">
         <v>240</v>
@@ -1794,13 +1770,13 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G25" s="2">
         <v>240</v>
@@ -1835,13 +1811,13 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F26" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G26" s="2">
         <v>240</v>
@@ -1876,13 +1852,13 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F27" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G27" s="2">
         <v>240</v>
@@ -1917,28 +1893,28 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="F28" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G28" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H28" s="2">
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="J28" s="2">
         <v>0</v>
       </c>
       <c r="K28" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="L28" s="2">
         <v>180</v>
@@ -1958,10 +1934,10 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F29" t="s">
         <v>23</v>
@@ -1999,37 +1975,37 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F30" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G30" s="2">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
       </c>
       <c r="K30" s="2">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="L30" s="2">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="M30" s="2">
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
@@ -2040,10 +2016,10 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s">
         <v>23</v>
@@ -2081,10 +2057,10 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="F32" t="s">
         <v>23</v>
@@ -2122,28 +2098,28 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G33" s="2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H33" s="2">
         <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
       </c>
       <c r="K33" s="2">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2">
         <v>180</v>
@@ -2163,16 +2139,16 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="F34" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G34" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H34" s="2">
         <v>0</v>
@@ -2187,13 +2163,13 @@
         <v>0</v>
       </c>
       <c r="L34" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M34" s="2">
         <v>0</v>
       </c>
       <c r="N34" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -2204,10 +2180,10 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="F35" t="s">
         <v>23</v>
@@ -2245,16 +2221,16 @@
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G36" s="2">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="H36" s="2">
         <v>0</v>
@@ -2269,13 +2245,13 @@
         <v>0</v>
       </c>
       <c r="L36" s="2">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="M36" s="2">
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -2286,10 +2262,10 @@
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="F37" t="s">
         <v>23</v>
@@ -2327,10 +2303,10 @@
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F38" t="s">
         <v>23</v>
@@ -2368,16 +2344,16 @@
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="F39" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="G39" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -2392,13 +2368,13 @@
         <v>0</v>
       </c>
       <c r="L39" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M39" s="2">
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
@@ -2409,10 +2385,10 @@
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D40" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F40" t="s">
         <v>23</v>
@@ -2450,16 +2426,16 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F41" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="G41" s="2">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H41" s="2">
         <v>0</v>
@@ -2474,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="L41" s="2">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="M41" s="2">
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -2491,16 +2467,16 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="D42" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="F42" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="G42" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -2515,13 +2491,13 @@
         <v>0</v>
       </c>
       <c r="L42" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M42" s="2">
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
@@ -2532,16 +2508,16 @@
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G43" s="2">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H43" s="2">
         <v>0</v>
@@ -2556,13 +2532,13 @@
         <v>0</v>
       </c>
       <c r="L43" s="2">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="M43" s="2">
         <v>0</v>
       </c>
       <c r="N43" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
@@ -2573,16 +2549,16 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="D44" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="F44" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="G44" s="2">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H44" s="2">
         <v>0</v>
@@ -2597,13 +2573,13 @@
         <v>0</v>
       </c>
       <c r="L44" s="2">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="M44" s="2">
         <v>0</v>
       </c>
       <c r="N44" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
@@ -2614,16 +2590,16 @@
         <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="D45" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G45" s="2">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -2638,145 +2614,22 @@
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="M45" s="2">
         <v>0</v>
       </c>
       <c r="N45" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="s">
-        <v>111</v>
-      </c>
-      <c r="D46" t="s">
-        <v>112</v>
-      </c>
-      <c r="F46" t="s">
-        <v>23</v>
-      </c>
-      <c r="G46" s="2">
-        <v>180</v>
-      </c>
-      <c r="H46" s="2">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2">
-        <v>0</v>
-      </c>
-      <c r="J46" s="2">
-        <v>0</v>
-      </c>
-      <c r="K46" s="2">
-        <v>0</v>
-      </c>
-      <c r="L46" s="2">
-        <v>180</v>
-      </c>
-      <c r="M46" s="2">
-        <v>0</v>
-      </c>
-      <c r="N46" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="s">
-        <v>123</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="K47" t="s">
         <v>124</v>
       </c>
-      <c r="F47" t="s">
-        <v>29</v>
-      </c>
-      <c r="G47" s="2">
-        <v>100</v>
-      </c>
-      <c r="H47" s="2">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2">
-        <v>0</v>
-      </c>
-      <c r="J47" s="2">
-        <v>0</v>
-      </c>
-      <c r="K47" s="2">
-        <v>0</v>
-      </c>
       <c r="L47" s="2">
-        <v>100</v>
-      </c>
-      <c r="M47" s="2">
-        <v>0</v>
-      </c>
-      <c r="N47" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="s">
-        <v>130</v>
-      </c>
-      <c r="D48" t="s">
-        <v>131</v>
-      </c>
-      <c r="F48" t="s">
-        <v>40</v>
-      </c>
-      <c r="G48" s="2">
-        <v>240</v>
-      </c>
-      <c r="H48" s="2">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2">
-        <v>-60</v>
-      </c>
-      <c r="J48" s="2">
-        <v>0</v>
-      </c>
-      <c r="K48" s="2">
-        <v>-60</v>
-      </c>
-      <c r="L48" s="2">
-        <v>180</v>
-      </c>
-      <c r="M48" s="2">
-        <v>0</v>
-      </c>
-      <c r="N48" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="50" spans="11:12" x14ac:dyDescent="0.2">
-      <c r="K50" t="s">
-        <v>132</v>
-      </c>
-      <c r="L50" s="2">
-        <f>SUM(L28:L48)</f>
-        <v>2710</v>
+        <f>SUM(L29:L45)</f>
+        <v>2530</v>
       </c>
     </row>
   </sheetData>

--- a/Fuerza Docente.xlsx
+++ b/Fuerza Docente.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC390EA-5438-704E-8186-4787FDA5985D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B8A1AF-9F77-9441-96A8-CEF81DDE8FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="25600" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -968,13 +968,14 @@
         <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="K5" s="2">
         <v>-60</v>
       </c>
       <c r="L5" s="2">
-        <v>180</v>
+        <f>G5+H5+I5+J5</f>
+        <v>164</v>
       </c>
       <c r="M5" s="2">
         <v>0</v>
@@ -1091,13 +1092,14 @@
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="K8" s="2">
         <v>-60</v>
       </c>
       <c r="L8" s="2">
-        <v>180</v>
+        <f>G8+H8+I8+J8</f>
+        <v>155</v>
       </c>
       <c r="M8" s="2">
         <v>0</v>

--- a/Fuerza Docente.xlsx
+++ b/Fuerza Docente.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B8A1AF-9F77-9441-96A8-CEF81DDE8FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA429F5-DA22-AB44-9C62-89D80B1D6E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="G23" s="2">
         <v>240</v>
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L23" s="2">
         <v>225</v>
@@ -1720,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
@@ -1731,10 +1731,10 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="F24" t="s">
         <v>67</v>
@@ -1772,10 +1772,10 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="F25" t="s">
         <v>67</v>
@@ -1784,7 +1784,7 @@
         <v>240</v>
       </c>
       <c r="H25" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
         <v>0</v>
@@ -1793,16 +1793,16 @@
         <v>0</v>
       </c>
       <c r="K25" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M25" s="2">
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -1813,10 +1813,10 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="F26" t="s">
         <v>67</v>
@@ -1854,19 +1854,19 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="F27" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="G27" s="2">
         <v>240</v>
       </c>
       <c r="H27" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="I27" s="2">
         <v>0</v>
@@ -1878,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="2">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="M27" s="2">
         <v>0</v>

--- a/Fuerza Docente.xlsx
+++ b/Fuerza Docente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA429F5-DA22-AB44-9C62-89D80B1D6E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF60A071-AE43-7640-873C-3332101BEC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="123">
   <si>
     <t>Fuerza Docente</t>
   </si>
@@ -381,15 +381,6 @@
   </si>
   <si>
     <t>Profesor/a Contratado/a Doctor/a - Tiempo completo, 8 horas lect. semanales</t>
-  </si>
-  <si>
-    <t>jorge.tredicce</t>
-  </si>
-  <si>
-    <t>TREDICCE, JORGE RAÚL</t>
-  </si>
-  <si>
-    <t>0.0 % (-100 h)</t>
   </si>
   <si>
     <t>elio.vtoranzo</t>
@@ -780,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -950,10 +941,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F5" t="s">
         <v>43</v>
@@ -1283,7 +1274,7 @@
         <v>76</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -1772,10 +1763,10 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F25" t="s">
         <v>67</v>
@@ -1895,10 +1886,10 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F28" t="s">
         <v>40</v>
@@ -2469,16 +2460,16 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="F42" t="s">
         <v>29</v>
       </c>
       <c r="G42" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -2493,13 +2484,13 @@
         <v>0</v>
       </c>
       <c r="L42" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="M42" s="2">
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
@@ -2510,10 +2501,10 @@
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="F43" t="s">
         <v>29</v>
@@ -2551,10 +2542,10 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D44" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F44" t="s">
         <v>29</v>
@@ -2584,54 +2575,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="s">
-        <v>61</v>
-      </c>
-      <c r="D45" t="s">
-        <v>62</v>
-      </c>
-      <c r="F45" t="s">
-        <v>29</v>
-      </c>
-      <c r="G45" s="2">
-        <v>60</v>
-      </c>
-      <c r="H45" s="2">
-        <v>0</v>
-      </c>
-      <c r="I45" s="2">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2">
-        <v>0</v>
-      </c>
-      <c r="K45" s="2">
-        <v>0</v>
-      </c>
-      <c r="L45" s="2">
-        <v>60</v>
-      </c>
-      <c r="M45" s="2">
-        <v>0</v>
-      </c>
-      <c r="N45" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="K47" t="s">
-        <v>124</v>
-      </c>
-      <c r="L47" s="2">
-        <f>SUM(L29:L45)</f>
-        <v>2530</v>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K46" t="s">
+        <v>121</v>
+      </c>
+      <c r="L46" s="2">
+        <f>SUM(L29:L44)</f>
+        <v>2430</v>
       </c>
     </row>
   </sheetData>

--- a/Fuerza Docente.xlsx
+++ b/Fuerza Docente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF60A071-AE43-7640-873C-3332101BEC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5811B76D-6B1B-2846-B668-8EFEF660517A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -155,9 +155,6 @@
     <t>pedro.chocano</t>
   </si>
   <si>
-    <t>CHOCANO FEITO, PEDRO JOSÉ</t>
-  </si>
-  <si>
     <t>Profesor/a Ayudante Doctor/a - Tiempo completo, 8 horas lect. semanales</t>
   </si>
   <si>
@@ -405,6 +402,9 @@
   </si>
   <si>
     <t>MUÑOZ MONTALVO, ANA I.</t>
+  </si>
+  <si>
+    <t>CHOCANO FEITO, PEDRO J.</t>
   </si>
 </sst>
 </file>
@@ -859,13 +859,13 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
         <v>41</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>42</v>
-      </c>
-      <c r="F3" t="s">
-        <v>43</v>
       </c>
       <c r="G3" s="2">
         <v>240</v>
@@ -889,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -900,13 +900,13 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" t="s">
         <v>98</v>
       </c>
-      <c r="D4" t="s">
-        <v>99</v>
-      </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G4" s="2">
         <v>240</v>
@@ -930,7 +930,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -941,13 +941,13 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" t="s">
         <v>117</v>
       </c>
-      <c r="D5" t="s">
-        <v>118</v>
-      </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2">
         <v>240</v>
@@ -983,13 +983,13 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
         <v>52</v>
       </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6" s="2">
         <v>240</v>
@@ -1013,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -1024,13 +1024,13 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
-        <v>46</v>
-      </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G7" s="2">
         <v>240</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -1065,13 +1065,13 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" t="s">
         <v>105</v>
       </c>
-      <c r="D8" t="s">
-        <v>106</v>
-      </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G8" s="2">
         <v>240</v>
@@ -1107,10 +1107,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
         <v>50</v>
-      </c>
-      <c r="D9" t="s">
-        <v>51</v>
       </c>
       <c r="F9" t="s">
         <v>19</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -1148,10 +1148,10 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
         <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>83</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -1189,10 +1189,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
         <v>101</v>
-      </c>
-      <c r="D11" t="s">
-        <v>102</v>
       </c>
       <c r="F11" t="s">
         <v>19</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -1230,10 +1230,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
         <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
       </c>
       <c r="F12" t="s">
         <v>19</v>
@@ -1271,10 +1271,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -1312,10 +1312,10 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s">
         <v>110</v>
-      </c>
-      <c r="D14" t="s">
-        <v>111</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
@@ -1353,10 +1353,10 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
         <v>80</v>
-      </c>
-      <c r="D15" t="s">
-        <v>81</v>
       </c>
       <c r="F15" t="s">
         <v>19</v>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -1394,10 +1394,10 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
         <v>89</v>
-      </c>
-      <c r="D16" t="s">
-        <v>90</v>
       </c>
       <c r="F16" t="s">
         <v>19</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -1435,10 +1435,10 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
         <v>58</v>
-      </c>
-      <c r="D17" t="s">
-        <v>59</v>
       </c>
       <c r="F17" t="s">
         <v>19</v>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -1476,10 +1476,10 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="s">
         <v>68</v>
-      </c>
-      <c r="D18" t="s">
-        <v>69</v>
       </c>
       <c r="F18" t="s">
         <v>19</v>
@@ -1517,10 +1517,10 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" t="s">
         <v>107</v>
-      </c>
-      <c r="D19" t="s">
-        <v>108</v>
       </c>
       <c r="F19" t="s">
         <v>19</v>
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -1599,10 +1599,10 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" t="s">
         <v>54</v>
-      </c>
-      <c r="D21" t="s">
-        <v>55</v>
       </c>
       <c r="F21" t="s">
         <v>19</v>
@@ -1681,13 +1681,13 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" t="s">
         <v>85</v>
       </c>
-      <c r="D23" t="s">
-        <v>86</v>
-      </c>
       <c r="F23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G23" s="2">
         <v>240</v>
@@ -1722,13 +1722,13 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
         <v>65</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>66</v>
-      </c>
-      <c r="F24" t="s">
-        <v>67</v>
       </c>
       <c r="G24" s="2">
         <v>240</v>
@@ -1763,13 +1763,13 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" t="s">
         <v>115</v>
       </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
       <c r="F25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G25" s="2">
         <v>240</v>
@@ -1804,13 +1804,13 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" t="s">
         <v>87</v>
       </c>
-      <c r="D26" t="s">
-        <v>88</v>
-      </c>
       <c r="F26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G26" s="2">
         <v>240</v>
@@ -1845,13 +1845,13 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" t="s">
         <v>112</v>
       </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
         <v>113</v>
-      </c>
-      <c r="F27" t="s">
-        <v>114</v>
       </c>
       <c r="G27" s="2">
         <v>240</v>
@@ -1886,13 +1886,13 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" t="s">
         <v>119</v>
       </c>
-      <c r="D28" t="s">
-        <v>120</v>
-      </c>
       <c r="F28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G28" s="2">
         <v>240</v>
@@ -1970,11 +1970,11 @@
       <c r="C30" t="s">
         <v>38</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" t="s">
         <v>39</v>
-      </c>
-      <c r="F30" t="s">
-        <v>40</v>
       </c>
       <c r="G30" s="2">
         <v>240</v>
@@ -2009,10 +2009,10 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" t="s">
         <v>72</v>
-      </c>
-      <c r="D31" t="s">
-        <v>73</v>
       </c>
       <c r="F31" t="s">
         <v>23</v>
@@ -2050,10 +2050,10 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" t="s">
         <v>63</v>
-      </c>
-      <c r="D32" t="s">
-        <v>64</v>
       </c>
       <c r="F32" t="s">
         <v>23</v>
@@ -2091,10 +2091,10 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" t="s">
         <v>96</v>
-      </c>
-      <c r="D33" t="s">
-        <v>97</v>
       </c>
       <c r="F33" t="s">
         <v>23</v>
@@ -2132,10 +2132,10 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
+        <v>102</v>
+      </c>
+      <c r="D34" t="s">
         <v>103</v>
-      </c>
-      <c r="D34" t="s">
-        <v>104</v>
       </c>
       <c r="F34" t="s">
         <v>23</v>
@@ -2173,10 +2173,10 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" t="s">
         <v>78</v>
-      </c>
-      <c r="D35" t="s">
-        <v>79</v>
       </c>
       <c r="F35" t="s">
         <v>23</v>
@@ -2296,10 +2296,10 @@
         <v>16</v>
       </c>
       <c r="C38" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" t="s">
         <v>56</v>
-      </c>
-      <c r="D38" t="s">
-        <v>57</v>
       </c>
       <c r="F38" t="s">
         <v>23</v>
@@ -2378,10 +2378,10 @@
         <v>16</v>
       </c>
       <c r="C40" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" t="s">
         <v>70</v>
-      </c>
-      <c r="D40" t="s">
-        <v>71</v>
       </c>
       <c r="F40" t="s">
         <v>23</v>
@@ -2419,13 +2419,13 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" t="s">
         <v>92</v>
       </c>
-      <c r="D41" t="s">
+      <c r="F41" t="s">
         <v>93</v>
-      </c>
-      <c r="F41" t="s">
-        <v>94</v>
       </c>
       <c r="G41" s="2">
         <v>90</v>
@@ -2449,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -2501,10 +2501,10 @@
         <v>16</v>
       </c>
       <c r="C43" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" t="s">
         <v>74</v>
-      </c>
-      <c r="D43" t="s">
-        <v>75</v>
       </c>
       <c r="F43" t="s">
         <v>29</v>
@@ -2542,10 +2542,10 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
+        <v>60</v>
+      </c>
+      <c r="D44" t="s">
         <v>61</v>
-      </c>
-      <c r="D44" t="s">
-        <v>62</v>
       </c>
       <c r="F44" t="s">
         <v>29</v>
@@ -2577,7 +2577,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="K46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L46" s="2">
         <f>SUM(L29:L44)</f>
